--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091F2F16-ECF7-4A64-A07E-503D015A152A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1D5A2F-1F0A-4FC4-8DF9-DE936C9813BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="24768" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -28,25 +28,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>специальной командой проектировщиков</t>
   </si>
   <si>
     <t>особым сообществом разработчиков</t>
+  </si>
+  <si>
+    <t>Моей первой невнятной реакцией</t>
+  </si>
+  <si>
+    <t>Моим первым невнятным ответов</t>
+  </si>
+  <si>
+    <t>армия тоже не располагает</t>
+  </si>
+  <si>
+    <t>вооружённые силы тоже не располагают</t>
+  </si>
+  <si>
+    <t>эта бесчеловечная тактика</t>
+  </si>
+  <si>
+    <t>этот бесчеловечный подход</t>
+  </si>
+  <si>
+    <t>обычную тактику бесполезной</t>
+  </si>
+  <si>
+    <t>обычный подход бесполезным</t>
+  </si>
+  <si>
+    <t>каждой истребительной группы</t>
+  </si>
+  <si>
+    <t>каждого истребительного подразделения</t>
+  </si>
+  <si>
+    <t>первую реальную атаку</t>
+  </si>
+  <si>
+    <t>первый настоящий удар</t>
+  </si>
+  <si>
+    <t>появилась новая группа</t>
+  </si>
+  <si>
+    <t>появилось новое подразделение</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -69,8 +118,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -351,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="36.3125" bestFit="1" customWidth="1"/>
@@ -366,6 +416,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1D5A2F-1F0A-4FC4-8DF9-DE936C9813BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F098BB-36EB-4640-A0A6-23F0AD253CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F098BB-36EB-4640-A0A6-23F0AD253CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3003DA00-C96A-4ABC-988C-D427251FB391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="3210" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -402,13 +402,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="36.3125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.47265625" customWidth="1"/>
+    <col min="1" max="1" width="36.29296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.46875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -424,7 +424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -448,7 +448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -456,7 +456,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -464,7 +464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>14</v>
       </c>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3003DA00-C96A-4ABC-988C-D427251FB391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB95B677-92F9-49EC-89A7-7FD402B70901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
+    <sheet name="Неизменные_короткие" sheetId="2" r:id="rId2"/>
+    <sheet name="неизменные" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>специальной командой проектировщиков</t>
   </si>
@@ -76,6 +78,24 @@
   </si>
   <si>
     <t>появилось новое подразделение</t>
+  </si>
+  <si>
+    <t>«Штрафная» тема долгое время была закрытой</t>
+  </si>
+  <si>
+    <t>«Исправительный» вопрос долгое время был закрытый</t>
+  </si>
+  <si>
+    <t>правдивая информация затушевывается, скрывается или представляется</t>
+  </si>
+  <si>
+    <t>правдивые сведения затушевываются, скрываются или представляются</t>
+  </si>
+  <si>
+    <t>«штрафную тему»</t>
+  </si>
+  <si>
+    <t>«исправительный вопрос»</t>
   </si>
 </sst>
 </file>
@@ -402,13 +422,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.29296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.46875" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -424,7 +444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -432,7 +452,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -440,7 +460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -448,7 +468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -456,7 +476,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -464,12 +484,64 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEAE8FF-D6D1-4BCA-92F8-1FC0A1E33D41}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="76.7109375" customWidth="1"/>
+    <col min="2" max="2" width="71" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB7E2CD-11F1-40F5-94BE-FB52DF54CD99}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="71.28515625" customWidth="1"/>
+    <col min="2" max="2" width="71.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,19 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB95B677-92F9-49EC-89A7-7FD402B70901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EE35F4-ECA5-46CF-87AD-44BAF0C35CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
     <sheet name="Неизменные_короткие" sheetId="2" r:id="rId2"/>
-    <sheet name="неизменные" sheetId="3" r:id="rId3"/>
+    <sheet name="составные" sheetId="4" r:id="rId3"/>
+    <sheet name="неизменные" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -30,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>специальной командой проектировщиков</t>
   </si>
@@ -96,6 +108,123 @@
   </si>
   <si>
     <t>«исправительный вопрос»</t>
+  </si>
+  <si>
+    <t>«штрафную» тему</t>
+  </si>
+  <si>
+    <t>«исправительный» вопрос</t>
+  </si>
+  <si>
+    <t>«штрафная» тема</t>
+  </si>
+  <si>
+    <t>«штрафная» тема стала модной</t>
+  </si>
+  <si>
+    <t>«исправительный» вопрос стал модным</t>
+  </si>
+  <si>
+    <t>другую «бумажную» информацию</t>
+  </si>
+  <si>
+    <t>другие «бумажные» сведения</t>
+  </si>
+  <si>
+    <t>другую «бумажную» информацию, которая честным критикам доступна</t>
+  </si>
+  <si>
+    <t>другие «бумажные» сведения, которые честным оценщикам доступны</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«штрафбатовскую» тему </t>
+  </si>
+  <si>
+    <t>штрафбатовской темы</t>
+  </si>
+  <si>
+    <t>штрафбатовского вопроса</t>
+  </si>
+  <si>
+    <t>известная всему миру трибуна</t>
+  </si>
+  <si>
+    <t>известный всему миру помост</t>
+  </si>
+  <si>
+    <t>«штрафное» положение</t>
+  </si>
+  <si>
+    <t>«исправительное» положение</t>
+  </si>
+  <si>
+    <t>в штрафбатовскую тему</t>
+  </si>
+  <si>
+    <t>в штрафбатовский вопрос</t>
+  </si>
+  <si>
+    <t>«штрафбатовское» время</t>
+  </si>
+  <si>
+    <t>«исправительное» время</t>
+  </si>
+  <si>
+    <t>слово «штрафной»</t>
+  </si>
+  <si>
+    <t>слово «исправительный»</t>
+  </si>
+  <si>
+    <t>штрафной майор</t>
+  </si>
+  <si>
+    <t>исправительный майор</t>
+  </si>
+  <si>
+    <t>штрафной (офицерский) батальон</t>
+  </si>
+  <si>
+    <t>исправительный (военачальствующий) батальон</t>
+  </si>
+  <si>
+    <t>Отдельного штрафного б-на</t>
+  </si>
+  <si>
+    <t>Отдельного исправительного батальона</t>
+  </si>
+  <si>
+    <t>штрафной капитан</t>
+  </si>
+  <si>
+    <t>исправительный капитан</t>
+  </si>
+  <si>
+    <t>Штрафного бна</t>
+  </si>
+  <si>
+    <t>исправительного батальона</t>
+  </si>
+  <si>
+    <t>не штрафная</t>
+  </si>
+  <si>
+    <t>не исправительная</t>
+  </si>
+  <si>
+    <t>штрафного офицерского б-на</t>
+  </si>
+  <si>
+    <t>штрафного б-на</t>
+  </si>
+  <si>
+    <t>штрафном офицерском батальоне</t>
+  </si>
+  <si>
+    <t>исправительного военачальствующего батальона</t>
+  </si>
+  <si>
+    <t>исправительном военачальствующим батальоне</t>
   </si>
 </sst>
 </file>
@@ -138,9 +267,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -421,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
@@ -492,6 +622,14 @@
         <v>15</v>
       </c>
     </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -499,7 +637,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEAE8FF-D6D1-4BCA-92F8-1FC0A1E33D41}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.7109375" customWidth="1"/>
@@ -514,14 +652,180 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED43094E-F29D-4F77-9E46-699CA581476C}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB7E2CD-11F1-40F5-94BE-FB52DF54CD99}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.28515625" customWidth="1"/>
@@ -544,6 +848,22 @@
         <v>19</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EE35F4-ECA5-46CF-87AD-44BAF0C35CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08509465-7205-421F-9370-DF39F9C7434D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
     <sheet name="Неизменные_короткие" sheetId="2" r:id="rId2"/>
-    <sheet name="составные" sheetId="4" r:id="rId3"/>
-    <sheet name="неизменные" sheetId="3" r:id="rId4"/>
+    <sheet name="простые" sheetId="5" r:id="rId3"/>
+    <sheet name="составные" sheetId="4" r:id="rId4"/>
+    <sheet name="неизменные" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="77">
   <si>
     <t>специальной командой проектировщиков</t>
   </si>
@@ -225,6 +226,54 @@
   </si>
   <si>
     <t>исправительном военачальствующим батальоне</t>
+  </si>
+  <si>
+    <t>переменный (штрафной)</t>
+  </si>
+  <si>
+    <t>переменный (исправительный)</t>
+  </si>
+  <si>
+    <t>й штрафной</t>
+  </si>
+  <si>
+    <t>й исправительный</t>
+  </si>
+  <si>
+    <t>доштрафное</t>
+  </si>
+  <si>
+    <t>до-исправительное</t>
+  </si>
+  <si>
+    <t>переменном (штрафном)</t>
+  </si>
+  <si>
+    <t>переменном (исправительном)</t>
+  </si>
+  <si>
+    <t>«штрафным» полком</t>
+  </si>
+  <si>
+    <t>«исправительным» полком</t>
+  </si>
+  <si>
+    <t>о дисциплине, вооружении</t>
+  </si>
+  <si>
+    <t>о правилах и их соблюдении, вооружении</t>
+  </si>
+  <si>
+    <t>Дисциплина у нас была железная</t>
+  </si>
+  <si>
+    <t>Соблюдение правл у нас было железное</t>
+  </si>
+  <si>
+    <t>формировать «гарнизон» и делал с ним</t>
+  </si>
+  <si>
+    <t>образовывать «воинскую часть» и делать с ней</t>
   </si>
 </sst>
 </file>
@@ -637,7 +686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEAE8FF-D6D1-4BCA-92F8-1FC0A1E33D41}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.7109375" customWidth="1"/>
@@ -782,10 +831,10 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
+      </c>
+      <c r="B18" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -794,6 +843,46 @@
       </c>
       <c r="B19" s="2" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -802,8 +891,30 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6931204F-D607-45BE-BF94-587C8B27C79D}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED43094E-F29D-4F77-9E46-699CA581476C}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -818,14 +929,22 @@
         <v>33</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB7E2CD-11F1-40F5-94BE-FB52DF54CD99}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.28515625" customWidth="1"/>
@@ -864,6 +983,22 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/словари/война.xlsx
+++ b/словари/война.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08509465-7205-421F-9370-DF39F9C7434D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F1FB7B-9214-4AF5-9BE3-92DA246E0DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Составные_важные" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
   <si>
     <t>специальной командой проектировщиков</t>
   </si>
@@ -686,7 +686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEAE8FF-D6D1-4BCA-92F8-1FC0A1E33D41}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.7109375" customWidth="1"/>
@@ -775,113 +775,105 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
+      <c r="A12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>49</v>
+      <c r="A13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" t="s">
-        <v>72</v>
+        <v>58</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="2" t="s">
         <v>74</v>
       </c>
     </row>
